--- a/erp-server/erp-server-file/src/main/resources/excel/wms/firstMilePackingBoxExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/firstMilePackingBoxExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>要货申请</t>
   </si>
@@ -55,6 +55,15 @@
     <t>数量</t>
   </si>
   <si>
+    <t>箱子包装尺寸长（cm）</t>
+  </si>
+  <si>
+    <t>箱子包装尺寸宽（cm）</t>
+  </si>
+  <si>
+    <t>箱子包装尺寸高（cm）</t>
+  </si>
+  <si>
     <t>{.deliveryCode}</t>
   </si>
   <si>
@@ -77,6 +86,15 @@
   </si>
   <si>
     <t>{.packQty}</t>
+  </si>
+  <si>
+    <t>{.length}</t>
+  </si>
+  <si>
+    <t>{.width}</t>
+  </si>
+  <si>
+    <t>{.height}</t>
   </si>
 </sst>
 </file>
@@ -1075,16 +1093,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="7"/>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="6" width="18.5" customWidth="1"/>
     <col min="7" max="7" width="16.5" customWidth="1"/>
     <col min="8" max="8" width="20.5" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
-    <col min="10" max="10" width="36.375" customWidth="1"/>
-    <col min="11" max="11" width="10.375" customWidth="1"/>
+    <col min="9" max="9" width="23.625" customWidth="1"/>
+    <col min="10" max="10" width="22.125" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
     <col min="13" max="13" width="8.875" customWidth="1"/>
     <col min="14" max="14" width="31.25" customWidth="1"/>
     <col min="16" max="16" width="17.375" customWidth="1"/>
@@ -1092,7 +1110,7 @@
     <col min="19" max="19" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1117,31 +1135,49 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:8">
+    <row r="2" s="1" customFormat="1" spans="1:11">
       <c r="A2" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/firstMilePackingBoxExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/firstMilePackingBoxExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
-    <t>要货申请</t>
+    <t>发货单</t>
   </si>
   <si>
     <t>FBA箱号</t>
